--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.21361662468274</v>
+        <v>11.24721270151095</v>
       </c>
       <c r="D2" t="n">
-        <v>36.46460929437269</v>
+        <v>5.925499010335563</v>
       </c>
       <c r="E2" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F2" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.24177275993311</v>
+        <v>5.564288073489131</v>
       </c>
       <c r="D3" t="n">
-        <v>31.52612467118994</v>
+        <v>5.122995259068365</v>
       </c>
       <c r="E3" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F3" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.0956994690763</v>
+        <v>1.803051163724899</v>
       </c>
       <c r="D4" t="n">
-        <v>8.88290758453906</v>
+        <v>1.443472482487597</v>
       </c>
       <c r="E4" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F4" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>71.51788921451785</v>
+        <v>11.62165699735915</v>
       </c>
       <c r="D5" t="n">
-        <v>40.01119717519407</v>
+        <v>6.501819540969037</v>
       </c>
       <c r="E5" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F5" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.02698833252301</v>
+        <v>8.29188560403499</v>
       </c>
       <c r="D6" t="n">
-        <v>20.21243308254589</v>
+        <v>3.284520375913708</v>
       </c>
       <c r="E6" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F6" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>74.05786124878902</v>
+        <v>12.03440245292822</v>
       </c>
       <c r="D7" t="n">
-        <v>47.56873750985141</v>
+        <v>7.729919845350854</v>
       </c>
       <c r="E7" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F7" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>74.96152280276614</v>
+        <v>12.1812474554495</v>
       </c>
       <c r="D8" t="n">
-        <v>71.91436964152167</v>
+        <v>11.68608506674727</v>
       </c>
       <c r="E8" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F8" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.49597939754398</v>
+        <v>3.980596652100896</v>
       </c>
       <c r="D9" t="n">
-        <v>24.07123296507009</v>
+        <v>3.91157535682389</v>
       </c>
       <c r="E9" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F9" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.05664750067264</v>
+        <v>7.971705218859304</v>
       </c>
       <c r="D10" t="n">
-        <v>49.84404244225395</v>
+        <v>8.099656896866268</v>
       </c>
       <c r="E10" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F10" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.14366970855062</v>
+        <v>6.035846327639476</v>
       </c>
       <c r="D11" t="n">
-        <v>36.01007029651868</v>
+        <v>5.851636423184285</v>
       </c>
       <c r="E11" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F11" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.11807772120197</v>
+        <v>1.969187629695319</v>
       </c>
       <c r="D12" t="n">
-        <v>12.13890834810357</v>
+        <v>1.972572606566831</v>
       </c>
       <c r="E12" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F12" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.84462662605473</v>
+        <v>7.287251826733893</v>
       </c>
       <c r="D13" t="n">
-        <v>43.80705866252846</v>
+        <v>7.118647032660875</v>
       </c>
       <c r="E13" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F13" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>57.51434052324541</v>
+        <v>9.346080335027379</v>
       </c>
       <c r="D14" t="n">
-        <v>58.5619273105863</v>
+        <v>9.516313187970274</v>
       </c>
       <c r="E14" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F14" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.571317828261407</v>
+        <v>1.555339147092479</v>
       </c>
       <c r="D15" t="n">
-        <v>10.17754309766318</v>
+        <v>1.653850753370266</v>
       </c>
       <c r="E15" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F15" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>65.75641861486095</v>
+        <v>10.6854180249149</v>
       </c>
       <c r="D16" t="n">
-        <v>64.94865714793512</v>
+        <v>10.55415678653946</v>
       </c>
       <c r="E16" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F16" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>58.72935834846915</v>
+        <v>9.543520731626236</v>
       </c>
       <c r="D17" t="n">
-        <v>59.86473941925117</v>
+        <v>9.728020155628315</v>
       </c>
       <c r="E17" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F17" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.33770153460559</v>
+        <v>4.929876499373409</v>
       </c>
       <c r="D18" t="n">
-        <v>30.06737006894896</v>
+        <v>4.885947636204206</v>
       </c>
       <c r="E18" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F18" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>68.75919540035083</v>
+        <v>11.17336925255701</v>
       </c>
       <c r="D19" t="n">
-        <v>69.89150325047891</v>
+        <v>11.35736927820282</v>
       </c>
       <c r="E19" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F19" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.71606559516616</v>
+        <v>7.7538606592145</v>
       </c>
       <c r="D20" t="n">
-        <v>48.83940918917824</v>
+        <v>7.936403993241465</v>
       </c>
       <c r="E20" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F20" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>43.37963928283534</v>
+        <v>7.049191383460744</v>
       </c>
       <c r="D21" t="n">
-        <v>43.05855042497737</v>
+        <v>6.997014444058823</v>
       </c>
       <c r="E21" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F21" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>64.4762465100773</v>
+        <v>10.47739005788756</v>
       </c>
       <c r="D22" t="n">
-        <v>65.61440158945805</v>
+        <v>10.66234025828693</v>
       </c>
       <c r="E22" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F22" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.72484048609265</v>
+        <v>6.130286578990055</v>
       </c>
       <c r="D23" t="n">
-        <v>38.65580362277705</v>
+        <v>6.281568088701271</v>
       </c>
       <c r="E23" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F23" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>78.78343448273981</v>
+        <v>12.80230810344522</v>
       </c>
       <c r="D24" t="n">
-        <v>79.92236188684728</v>
+        <v>12.98738380661268</v>
       </c>
       <c r="E24" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F24" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>44.44185573866737</v>
+        <v>7.221801557533448</v>
       </c>
       <c r="D25" t="n">
-        <v>44.83855491904301</v>
+        <v>7.286265174344488</v>
       </c>
       <c r="E25" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F25" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>56.65625513176588</v>
+        <v>9.206641458911957</v>
       </c>
       <c r="D26" t="n">
-        <v>57.24149511143538</v>
+        <v>9.301742955608249</v>
       </c>
       <c r="E26" t="n">
-        <v>20.09991960946237</v>
+        <v>3.266236936537635</v>
       </c>
       <c r="F26" t="n">
-        <v>19.21017678486833</v>
+        <v>3.121653727541103</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
